--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2353,6 +2353,302 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>late start maintenance</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AUTO TIE BALER</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Darius</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>LD was supersack w/loose LD bales</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tony left early, Jay had to sort pallets, cut pallets, and load on the belt</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>finished HD - opened up shredder and granulator and cleaned them out - switched to LD purge</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Darius, Clarnce</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>machine was overheating</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>single shaft thermal cut off alarm kept appearing - had to reset machine before blowing a fuse</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>started at 1030 - it went down on second shift yesterday - got it going for a couple of hours and another fuse blew</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>had to do a blade change - hand feeing the grinder waiting on maintenance to finish the shredder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,6 +2649,80 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no weights entered - late start, had to wait for material</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>the first 3.5 hours were spent jumping in and out of the machine - the modifications were made for regular sized plastic pallets - the pallets that were run were a lot longer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2723,6 +2723,154 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Clarence had to keep jumping in and out of machine</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>belt under shredder stopped working</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>came in and the belt for the shredder was not working - switching material - Chad is going to help with new material</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>downtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>switching from HDPE to HIPS</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2871,6 +2871,39 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no info given - Tim is out</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/aggregated_notes.xlsx
+++ b/data/aggregated_notes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2904,6 +2904,117 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>finished crates and started pallets - guillotine can't keep up</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Clarence</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>start time was 0945</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HDPE</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>finished the pallets and started the green grass regrinds</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
